--- a/tabela_frei_galvao.xlsx
+++ b/tabela_frei_galvao.xlsx
@@ -3336,7 +3336,7 @@
     <xdr:ext cx="971550" cy="247650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png"/>
+        <xdr:cNvPr id="0" name="image4.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3364,7 +3364,7 @@
     <xdr:ext cx="1076325" cy="514350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3389,10 +3389,10 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="390525" cy="361950"/>
+    <xdr:ext cx="400050" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3420,7 +3420,7 @@
     <xdr:ext cx="514350" cy="257175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3862,7 +3862,7 @@
         <v>163001.47</v>
       </c>
       <c r="I13" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="14" ht="12.0" customHeight="1">
@@ -3891,7 +3891,7 @@
         <v>122689.28</v>
       </c>
       <c r="I14" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
@@ -3920,7 +3920,7 @@
         <v>122689.28</v>
       </c>
       <c r="I15" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="16" ht="12.0" customHeight="1">
@@ -3949,7 +3949,7 @@
         <v>163001.47</v>
       </c>
       <c r="I16" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="17" ht="12.0" customHeight="1">
@@ -3978,7 +3978,7 @@
         <v>128531.63</v>
       </c>
       <c r="I17" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="18" ht="12.0" customHeight="1">
@@ -4007,7 +4007,7 @@
         <v>128531.63</v>
       </c>
       <c r="I18" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="19" ht="12.0" customHeight="1">
@@ -4036,7 +4036,7 @@
         <v>128531.63</v>
       </c>
       <c r="I19" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="20" ht="12.0" customHeight="1">
@@ -4065,7 +4065,7 @@
         <v>128531.63</v>
       </c>
       <c r="I20" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="21" ht="12.0" customHeight="1">
@@ -4094,7 +4094,7 @@
         <v>128531.63</v>
       </c>
       <c r="I21" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="22" ht="12.0" customHeight="1">
@@ -4123,7 +4123,7 @@
         <v>128531.63</v>
       </c>
       <c r="I22" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="23" ht="12.0" customHeight="1">
@@ -4152,7 +4152,7 @@
         <v>128531.63</v>
       </c>
       <c r="I23" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
@@ -4181,7 +4181,7 @@
         <v>128531.63</v>
       </c>
       <c r="I24" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="25" ht="12.0" customHeight="1">
@@ -4210,7 +4210,7 @@
         <v>128531.63</v>
       </c>
       <c r="I25" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="26" ht="12.0" customHeight="1">
@@ -4239,7 +4239,7 @@
         <v>128531.63</v>
       </c>
       <c r="I26" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="27" ht="12.0" customHeight="1">
@@ -4268,7 +4268,7 @@
         <v>128531.63</v>
       </c>
       <c r="I27" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="28" ht="12.0" customHeight="1">
@@ -4297,7 +4297,7 @@
         <v>128531.63</v>
       </c>
       <c r="I28" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="29" ht="12.0" customHeight="1">
@@ -4326,7 +4326,7 @@
         <v>128531.63</v>
       </c>
       <c r="I29" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="30" ht="12.0" customHeight="1">
@@ -4355,7 +4355,7 @@
         <v>128531.63</v>
       </c>
       <c r="I30" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="31" ht="12.0" customHeight="1">
@@ -4384,7 +4384,7 @@
         <v>128531.63</v>
       </c>
       <c r="I31" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
@@ -4413,7 +4413,7 @@
         <v>192797.44</v>
       </c>
       <c r="I32" s="22">
-        <v>205623.46</v>
+        <v>203587.58</v>
       </c>
     </row>
     <row r="33" ht="12.0" customHeight="1">
@@ -4442,7 +4442,7 @@
         <v>192797.44</v>
       </c>
       <c r="I33" s="22">
-        <v>205623.46</v>
+        <v>203587.58</v>
       </c>
     </row>
     <row r="34" ht="12.0" customHeight="1">
@@ -4471,7 +4471,7 @@
         <v>163001.47</v>
       </c>
       <c r="I34" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="35" ht="12.0" customHeight="1">
@@ -4500,7 +4500,7 @@
         <v>163001.47</v>
       </c>
       <c r="I35" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="36" ht="12.0" customHeight="1">
@@ -4529,7 +4529,7 @@
         <v>163001.47</v>
       </c>
       <c r="I36" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="37" ht="12.0" customHeight="1">
@@ -4558,7 +4558,7 @@
         <v>163001.47</v>
       </c>
       <c r="I37" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="38" ht="12.0" customHeight="1">
@@ -4587,7 +4587,7 @@
         <v>163001.47</v>
       </c>
       <c r="I38" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="39" ht="12.0" customHeight="1">
@@ -4616,7 +4616,7 @@
         <v>163001.47</v>
       </c>
       <c r="I39" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
@@ -4645,7 +4645,7 @@
         <v>163001.47</v>
       </c>
       <c r="I40" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="41" ht="12.0" customHeight="1">
@@ -4674,7 +4674,7 @@
         <v>163001.47</v>
       </c>
       <c r="I41" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="42" ht="12.0" customHeight="1">
@@ -4703,7 +4703,7 @@
         <v>163001.47</v>
       </c>
       <c r="I42" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="43" ht="12.0" customHeight="1">
@@ -4732,7 +4732,7 @@
         <v>178775.81</v>
       </c>
       <c r="I43" s="22">
-        <v>190669.03</v>
+        <v>188781.21</v>
       </c>
     </row>
     <row r="44" ht="12.0" customHeight="1">
@@ -4761,7 +4761,7 @@
         <v>163001.47</v>
       </c>
       <c r="I44" s="22">
-        <v>173845.29</v>
+        <v>172124.05</v>
       </c>
     </row>
     <row r="45" ht="12.0" customHeight="1">
@@ -4790,7 +4790,7 @@
         <v>178927.24</v>
       </c>
       <c r="I45" s="22">
-        <v>190830.53</v>
+        <v>188941.12</v>
       </c>
     </row>
     <row r="46" ht="12.0" customHeight="1">
@@ -4819,7 +4819,7 @@
         <v>128531.63</v>
       </c>
       <c r="I46" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="47" ht="12.0" customHeight="1">
@@ -4848,7 +4848,7 @@
         <v>128531.63</v>
       </c>
       <c r="I47" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="48" ht="12.0" customHeight="1">
@@ -4877,7 +4877,7 @@
         <v>128531.63</v>
       </c>
       <c r="I48" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
@@ -4906,7 +4906,7 @@
         <v>128531.63</v>
       </c>
       <c r="I49" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="50" ht="12.0" customHeight="1">
@@ -4935,7 +4935,7 @@
         <v>128531.63</v>
       </c>
       <c r="I50" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="51" ht="12.0" customHeight="1">
@@ -4964,7 +4964,7 @@
         <v>128531.63</v>
       </c>
       <c r="I51" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="52" ht="12.0" customHeight="1">
@@ -4993,7 +4993,7 @@
         <v>128531.63</v>
       </c>
       <c r="I52" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="53" ht="12.0" customHeight="1">
@@ -5022,7 +5022,7 @@
         <v>128531.63</v>
       </c>
       <c r="I53" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="54" ht="12.0" customHeight="1">
@@ -5051,7 +5051,7 @@
         <v>128531.63</v>
       </c>
       <c r="I54" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="55" ht="12.0" customHeight="1">
@@ -5080,7 +5080,7 @@
         <v>128531.63</v>
       </c>
       <c r="I55" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="56" ht="12.0" customHeight="1">
@@ -5109,7 +5109,7 @@
         <v>128531.63</v>
       </c>
       <c r="I56" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
@@ -5138,7 +5138,7 @@
         <v>128531.63</v>
       </c>
       <c r="I57" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="58" ht="12.0" customHeight="1">
@@ -5167,7 +5167,7 @@
         <v>128531.63</v>
       </c>
       <c r="I58" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="59" ht="11.25" customHeight="1">
@@ -5196,7 +5196,7 @@
         <v>128531.63</v>
       </c>
       <c r="I59" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="60" ht="12.0" customHeight="1">
@@ -5225,7 +5225,7 @@
         <v>128531.63</v>
       </c>
       <c r="I60" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="61" ht="12.0" customHeight="1">
@@ -5254,7 +5254,7 @@
         <v>128531.63</v>
       </c>
       <c r="I61" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="62" ht="12.0" customHeight="1">
@@ -5283,7 +5283,7 @@
         <v>162806.73</v>
       </c>
       <c r="I62" s="22">
-        <v>173637.59</v>
+        <v>171918.4</v>
       </c>
     </row>
     <row r="63" ht="12.0" customHeight="1">
@@ -5312,7 +5312,7 @@
         <v>162806.73</v>
       </c>
       <c r="I63" s="22">
-        <v>173637.59</v>
+        <v>171918.4</v>
       </c>
     </row>
     <row r="64" ht="12.0" customHeight="1">
@@ -5341,7 +5341,7 @@
         <v>128531.63</v>
       </c>
       <c r="I64" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
@@ -5370,7 +5370,7 @@
         <v>128531.63</v>
       </c>
       <c r="I65" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="66" ht="12.0" customHeight="1">
@@ -5399,7 +5399,7 @@
         <v>128531.63</v>
       </c>
       <c r="I66" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="67" ht="12.0" customHeight="1">
@@ -5428,7 +5428,7 @@
         <v>128531.63</v>
       </c>
       <c r="I67" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="68" ht="12.0" customHeight="1">
@@ -5457,7 +5457,7 @@
         <v>128531.63</v>
       </c>
       <c r="I68" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="69" ht="12.0" customHeight="1">
@@ -5486,7 +5486,7 @@
         <v>128531.63</v>
       </c>
       <c r="I69" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="70" ht="12.0" customHeight="1">
@@ -5515,7 +5515,7 @@
         <v>128531.63</v>
       </c>
       <c r="I70" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="71" ht="12.0" customHeight="1">
@@ -5544,7 +5544,7 @@
         <v>128531.63</v>
       </c>
       <c r="I71" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="72" ht="12.0" customHeight="1">
@@ -5573,7 +5573,7 @@
         <v>128531.63</v>
       </c>
       <c r="I72" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
@@ -5602,7 +5602,7 @@
         <v>128531.63</v>
       </c>
       <c r="I73" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="74" ht="12.0" customHeight="1">
@@ -5631,7 +5631,7 @@
         <v>128531.63</v>
       </c>
       <c r="I74" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="75" ht="12.0" customHeight="1">
@@ -5660,7 +5660,7 @@
         <v>128531.63</v>
       </c>
       <c r="I75" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="76" ht="12.0" customHeight="1">
@@ -5689,7 +5689,7 @@
         <v>128531.63</v>
       </c>
       <c r="I76" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="77" ht="12.0" customHeight="1">
@@ -5718,7 +5718,7 @@
         <v>128531.63</v>
       </c>
       <c r="I77" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="78" ht="12.0" customHeight="1">
@@ -5747,7 +5747,7 @@
         <v>128531.63</v>
       </c>
       <c r="I78" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="79" ht="12.0" customHeight="1">
@@ -5776,7 +5776,7 @@
         <v>128531.63</v>
       </c>
       <c r="I79" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="80" ht="12.0" customHeight="1">
@@ -5805,7 +5805,7 @@
         <v>181112.75</v>
       </c>
       <c r="I80" s="22">
-        <v>193161.43</v>
+        <v>191248.94</v>
       </c>
     </row>
     <row r="81" ht="12.0" customHeight="1">
@@ -5834,7 +5834,7 @@
         <v>116846.93</v>
       </c>
       <c r="I81" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
@@ -5863,7 +5863,7 @@
         <v>116846.93</v>
       </c>
       <c r="I82" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="83" ht="12.0" customHeight="1">
@@ -5892,7 +5892,7 @@
         <v>181112.75</v>
       </c>
       <c r="I83" s="22">
-        <v>193161.43</v>
+        <v>191248.94</v>
       </c>
     </row>
     <row r="84" ht="12.0" customHeight="1">
@@ -5921,7 +5921,7 @@
         <v>116846.93</v>
       </c>
       <c r="I84" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="85" ht="12.0" customHeight="1">
@@ -5950,7 +5950,7 @@
         <v>116846.93</v>
       </c>
       <c r="I85" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="86" ht="12.0" customHeight="1">
@@ -5979,7 +5979,7 @@
         <v>116846.93</v>
       </c>
       <c r="I86" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="87" ht="12.0" customHeight="1">
@@ -6008,7 +6008,7 @@
         <v>116846.93</v>
       </c>
       <c r="I87" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="88" ht="12.0" customHeight="1">
@@ -6037,7 +6037,7 @@
         <v>191174.57</v>
       </c>
       <c r="I88" s="22">
-        <v>203892.62</v>
+        <v>201873.88</v>
       </c>
     </row>
     <row r="89" ht="12.0" customHeight="1">
@@ -6066,7 +6066,7 @@
         <v>116846.93</v>
       </c>
       <c r="I89" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="90" ht="12.75" customHeight="1">
@@ -6095,7 +6095,7 @@
         <v>116846.93</v>
       </c>
       <c r="I90" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="91" ht="12.0" customHeight="1">
@@ -6124,7 +6124,7 @@
         <v>191174.57</v>
       </c>
       <c r="I91" s="22">
-        <v>203892.62</v>
+        <v>201873.88</v>
       </c>
     </row>
     <row r="92" ht="12.0" customHeight="1">
@@ -6153,7 +6153,7 @@
         <v>116846.93</v>
       </c>
       <c r="I92" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="93" ht="12.0" customHeight="1">
@@ -6182,7 +6182,7 @@
         <v>116846.93</v>
       </c>
       <c r="I93" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="94" ht="12.0" customHeight="1">
@@ -6211,7 +6211,7 @@
         <v>116846.93</v>
       </c>
       <c r="I94" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="95" ht="12.0" customHeight="1">
@@ -6240,7 +6240,7 @@
         <v>116846.93</v>
       </c>
       <c r="I95" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="96" ht="12.0" customHeight="1">
@@ -6269,7 +6269,7 @@
         <v>181112.75</v>
       </c>
       <c r="I96" s="22">
-        <v>193161.43</v>
+        <v>191248.94</v>
       </c>
     </row>
     <row r="97" ht="12.0" customHeight="1">
@@ -6298,7 +6298,7 @@
         <v>116846.93</v>
       </c>
       <c r="I97" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
@@ -6327,7 +6327,7 @@
         <v>116846.93</v>
       </c>
       <c r="I98" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="99" ht="12.0" customHeight="1">
@@ -6356,7 +6356,7 @@
         <v>181112.75</v>
       </c>
       <c r="I99" s="22">
-        <v>193161.43</v>
+        <v>191248.94</v>
       </c>
     </row>
     <row r="100" ht="12.0" customHeight="1">
@@ -6385,7 +6385,7 @@
         <v>116846.93</v>
       </c>
       <c r="I100" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="101" ht="12.0" customHeight="1">
@@ -6414,7 +6414,7 @@
         <v>116846.93</v>
       </c>
       <c r="I101" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="102" ht="12.0" customHeight="1">
@@ -6443,7 +6443,7 @@
         <v>116846.93</v>
       </c>
       <c r="I102" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="103" ht="12.0" customHeight="1">
@@ -6472,7 +6472,7 @@
         <v>116846.93</v>
       </c>
       <c r="I103" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="104" ht="12.0" customHeight="1">
@@ -6501,7 +6501,7 @@
         <v>116846.93</v>
       </c>
       <c r="I104" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="105" ht="12.0" customHeight="1">
@@ -6530,7 +6530,7 @@
         <v>116846.93</v>
       </c>
       <c r="I105" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="106" ht="12.0" customHeight="1">
@@ -6559,7 +6559,7 @@
         <v>116846.93</v>
       </c>
       <c r="I106" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
@@ -6588,7 +6588,7 @@
         <v>191174.57</v>
       </c>
       <c r="I107" s="22">
-        <v>203892.62</v>
+        <v>201873.88</v>
       </c>
     </row>
     <row r="108" ht="12.0" customHeight="1">
@@ -6617,7 +6617,7 @@
         <v>116846.93</v>
       </c>
       <c r="I108" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="109" ht="12.0" customHeight="1">
@@ -6646,7 +6646,7 @@
         <v>116846.93</v>
       </c>
       <c r="I109" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="110" ht="12.0" customHeight="1">
@@ -6675,7 +6675,7 @@
         <v>191174.57</v>
       </c>
       <c r="I110" s="22">
-        <v>203892.62</v>
+        <v>201873.88</v>
       </c>
     </row>
     <row r="111" ht="12.0" customHeight="1">
@@ -6704,7 +6704,7 @@
         <v>116846.93</v>
       </c>
       <c r="I111" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="112" ht="12.0" customHeight="1">
@@ -6733,7 +6733,7 @@
         <v>116846.93</v>
       </c>
       <c r="I112" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="113" ht="12.0" customHeight="1">
@@ -6762,7 +6762,7 @@
         <v>116846.93</v>
       </c>
       <c r="I113" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="114" ht="12.0" customHeight="1">
@@ -6791,7 +6791,7 @@
         <v>116846.93</v>
       </c>
       <c r="I114" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
@@ -6820,7 +6820,7 @@
         <v>116846.93</v>
       </c>
       <c r="I115" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="116" ht="12.0" customHeight="1">
@@ -6849,7 +6849,7 @@
         <v>116846.93</v>
       </c>
       <c r="I116" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="117" ht="12.0" customHeight="1">
@@ -6878,7 +6878,7 @@
         <v>116846.93</v>
       </c>
       <c r="I117" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="118" ht="12.0" customHeight="1">
@@ -6907,7 +6907,7 @@
         <v>148006.12</v>
       </c>
       <c r="I118" s="22">
-        <v>157852.35</v>
+        <v>156289.46</v>
       </c>
     </row>
     <row r="119" ht="12.0" customHeight="1">
@@ -6936,7 +6936,7 @@
         <v>116846.93</v>
       </c>
       <c r="I119" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="120" ht="12.0" customHeight="1">
@@ -6965,7 +6965,7 @@
         <v>116846.93</v>
       </c>
       <c r="I120" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="121" ht="12.0" customHeight="1">
@@ -6994,7 +6994,7 @@
         <v>116846.93</v>
       </c>
       <c r="I121" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="122" ht="12.0" customHeight="1">
@@ -7023,7 +7023,7 @@
         <v>116846.93</v>
       </c>
       <c r="I122" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="123" ht="12.0" customHeight="1">
@@ -7052,7 +7052,7 @@
         <v>116846.93</v>
       </c>
       <c r="I123" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="124" ht="12.0" customHeight="1">
@@ -7081,7 +7081,7 @@
         <v>116846.93</v>
       </c>
       <c r="I124" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="125" ht="12.0" customHeight="1">
@@ -7110,7 +7110,7 @@
         <v>116846.93</v>
       </c>
       <c r="I125" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="126" ht="12.0" customHeight="1">
@@ -7139,7 +7139,7 @@
         <v>116846.93</v>
       </c>
       <c r="I126" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="127" ht="12.0" customHeight="1">
@@ -7168,7 +7168,7 @@
         <v>116846.93</v>
       </c>
       <c r="I127" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="128" ht="12.75" customHeight="1">
@@ -7197,7 +7197,7 @@
         <v>116846.93</v>
       </c>
       <c r="I128" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="129" ht="12.0" customHeight="1">
@@ -7226,7 +7226,7 @@
         <v>116846.93</v>
       </c>
       <c r="I129" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="130" ht="12.0" customHeight="1">
@@ -7255,7 +7255,7 @@
         <v>116846.93</v>
       </c>
       <c r="I130" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="131" ht="12.0" customHeight="1">
@@ -7284,7 +7284,7 @@
         <v>116846.93</v>
       </c>
       <c r="I131" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="132" ht="12.0" customHeight="1">
@@ -7313,7 +7313,7 @@
         <v>116846.93</v>
       </c>
       <c r="I132" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="133" ht="12.0" customHeight="1">
@@ -7342,7 +7342,7 @@
         <v>148006.12</v>
       </c>
       <c r="I133" s="22">
-        <v>157852.35</v>
+        <v>156289.46</v>
       </c>
     </row>
     <row r="134" ht="12.0" customHeight="1">
@@ -7371,7 +7371,7 @@
         <v>148006.12</v>
       </c>
       <c r="I134" s="22">
-        <v>157852.35</v>
+        <v>156289.46</v>
       </c>
     </row>
     <row r="135" ht="12.0" customHeight="1">
@@ -7400,7 +7400,7 @@
         <v>116846.93</v>
       </c>
       <c r="I135" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="136" ht="12.75" customHeight="1">
@@ -7429,7 +7429,7 @@
         <v>116846.93</v>
       </c>
       <c r="I136" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="137" ht="12.0" customHeight="1">
@@ -7458,7 +7458,7 @@
         <v>116846.93</v>
       </c>
       <c r="I137" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="138" ht="12.0" customHeight="1">
@@ -7487,7 +7487,7 @@
         <v>116846.93</v>
       </c>
       <c r="I138" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="139" ht="12.0" customHeight="1">
@@ -7516,7 +7516,7 @@
         <v>116846.93</v>
       </c>
       <c r="I139" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="140" ht="12.0" customHeight="1">
@@ -7545,7 +7545,7 @@
         <v>116846.93</v>
       </c>
       <c r="I140" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="141" ht="12.0" customHeight="1">
@@ -7574,7 +7574,7 @@
         <v>116846.93</v>
       </c>
       <c r="I141" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="142" ht="12.0" customHeight="1">
@@ -7603,7 +7603,7 @@
         <v>116846.93</v>
       </c>
       <c r="I142" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="143" ht="12.0" customHeight="1">
@@ -7632,7 +7632,7 @@
         <v>116846.93</v>
       </c>
       <c r="I143" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="144" ht="12.0" customHeight="1">
@@ -7661,7 +7661,7 @@
         <v>116846.93</v>
       </c>
       <c r="I144" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="145" ht="12.75" customHeight="1">
@@ -7690,7 +7690,7 @@
         <v>116846.93</v>
       </c>
       <c r="I145" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="146" ht="12.0" customHeight="1">
@@ -7719,7 +7719,7 @@
         <v>116846.93</v>
       </c>
       <c r="I146" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="147" ht="12.0" customHeight="1">
@@ -7748,7 +7748,7 @@
         <v>116846.93</v>
       </c>
       <c r="I147" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="148" ht="12.0" customHeight="1">
@@ -7777,7 +7777,7 @@
         <v>116846.93</v>
       </c>
       <c r="I148" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="149" ht="12.0" customHeight="1">
@@ -7806,7 +7806,7 @@
         <v>148006.12</v>
       </c>
       <c r="I149" s="22">
-        <v>157852.35</v>
+        <v>156289.46</v>
       </c>
     </row>
     <row r="150" ht="12.0" customHeight="1">
@@ -7835,7 +7835,7 @@
         <v>196297.66</v>
       </c>
       <c r="I150" s="22">
-        <v>209356.53</v>
+        <v>207283.69</v>
       </c>
     </row>
     <row r="151" ht="12.0" customHeight="1">
@@ -7864,7 +7864,7 @@
         <v>127441.06</v>
       </c>
       <c r="I151" s="22">
-        <v>135919.18</v>
+        <v>134573.45</v>
       </c>
     </row>
     <row r="152" ht="12.0" customHeight="1">
@@ -7893,7 +7893,7 @@
         <v>124995.06</v>
       </c>
       <c r="I152" s="22">
-        <v>133310.47</v>
+        <v>131990.56</v>
       </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
@@ -7922,7 +7922,7 @@
         <v>168893.16</v>
       </c>
       <c r="I153" s="22">
-        <v>180128.92</v>
+        <v>178345.46</v>
       </c>
     </row>
     <row r="154" ht="12.0" customHeight="1">
@@ -7951,7 +7951,7 @@
         <v>116846.93</v>
       </c>
       <c r="I154" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="155" ht="12.0" customHeight="1">
@@ -7980,7 +7980,7 @@
         <v>116846.93</v>
       </c>
       <c r="I155" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="156" ht="12.0" customHeight="1">
@@ -8009,7 +8009,7 @@
         <v>116846.93</v>
       </c>
       <c r="I156" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="157" ht="12.0" customHeight="1">
@@ -8038,7 +8038,7 @@
         <v>116846.93</v>
       </c>
       <c r="I157" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="158" ht="12.0" customHeight="1">
@@ -8067,7 +8067,7 @@
         <v>116846.93</v>
       </c>
       <c r="I158" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="159" ht="12.0" customHeight="1">
@@ -8096,7 +8096,7 @@
         <v>116846.93</v>
       </c>
       <c r="I159" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="160" ht="12.0" customHeight="1">
@@ -8125,7 +8125,7 @@
         <v>116846.93</v>
       </c>
       <c r="I160" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="161" ht="12.75" customHeight="1">
@@ -8154,7 +8154,7 @@
         <v>155795.91</v>
       </c>
       <c r="I161" s="22">
-        <v>166160.37</v>
+        <v>164515.22</v>
       </c>
     </row>
     <row r="162" ht="12.0" customHeight="1">
@@ -8183,7 +8183,7 @@
         <v>155795.91</v>
       </c>
       <c r="I162" s="22">
-        <v>166160.37</v>
+        <v>164515.22</v>
       </c>
     </row>
     <row r="163" ht="12.0" customHeight="1">
@@ -8212,7 +8212,7 @@
         <v>116846.93</v>
       </c>
       <c r="I163" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="164" ht="12.0" customHeight="1">
@@ -8241,7 +8241,7 @@
         <v>116846.93</v>
       </c>
       <c r="I164" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="165" ht="12.0" customHeight="1">
@@ -8270,7 +8270,7 @@
         <v>116846.93</v>
       </c>
       <c r="I165" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="166" ht="12.0" customHeight="1">
@@ -8299,7 +8299,7 @@
         <v>116846.93</v>
       </c>
       <c r="I166" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="167" ht="12.0" customHeight="1">
@@ -8328,7 +8328,7 @@
         <v>116846.93</v>
       </c>
       <c r="I167" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="168" ht="12.0" customHeight="1">
@@ -8357,7 +8357,7 @@
         <v>116846.93</v>
       </c>
       <c r="I168" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="169" ht="12.0" customHeight="1">
@@ -8386,7 +8386,7 @@
         <v>116846.93</v>
       </c>
       <c r="I169" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="170" ht="11.25" customHeight="1">
@@ -8415,7 +8415,7 @@
         <v>116846.93</v>
       </c>
       <c r="I170" s="22">
-        <v>124620.28</v>
+        <v>123386.41</v>
       </c>
     </row>
     <row r="171" ht="11.25" customHeight="1">
@@ -8444,7 +8444,7 @@
         <v>226572.75</v>
       </c>
       <c r="I171" s="22">
-        <v>241645.7</v>
+        <v>239253.17</v>
       </c>
     </row>
     <row r="172" ht="11.25" customHeight="1">
@@ -8473,7 +8473,7 @@
         <v>132543.68</v>
       </c>
       <c r="I172" s="22">
-        <v>141361.27</v>
+        <v>139961.65</v>
       </c>
     </row>
     <row r="173" ht="11.25" customHeight="1">
@@ -8502,7 +8502,7 @@
         <v>216613.65</v>
       </c>
       <c r="I173" s="22">
-        <v>231024.06</v>
+        <v>228736.7</v>
       </c>
     </row>
     <row r="174" ht="11.25" customHeight="1">
@@ -8531,7 +8531,7 @@
         <v>127343.84</v>
       </c>
       <c r="I174" s="22">
-        <v>135815.5</v>
+        <v>134470.79</v>
       </c>
     </row>
     <row r="175" ht="11.25" customHeight="1">
@@ -8560,7 +8560,7 @@
         <v>129634.04</v>
       </c>
       <c r="I175" s="22">
-        <v>138258.06</v>
+        <v>136889.17</v>
       </c>
     </row>
     <row r="176" ht="11.25" customHeight="1">
@@ -8589,7 +8589,7 @@
         <v>149299.22</v>
       </c>
       <c r="I176" s="22">
-        <v>159231.48</v>
+        <v>157654.93</v>
       </c>
     </row>
     <row r="177" ht="11.25" customHeight="1">
@@ -8618,7 +8618,7 @@
         <v>144147.36</v>
       </c>
       <c r="I177" s="22">
-        <v>153736.89</v>
+        <v>152214.74</v>
       </c>
     </row>
     <row r="178" ht="11.25" customHeight="1">
@@ -8647,7 +8647,7 @@
         <v>164301.12</v>
       </c>
       <c r="I178" s="22">
-        <v>175231.4</v>
+        <v>173496.43</v>
       </c>
     </row>
     <row r="179" ht="11.25" customHeight="1">
@@ -8676,7 +8676,7 @@
         <v>122144.0</v>
       </c>
       <c r="I179" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="180" ht="11.25" customHeight="1">
@@ -8705,7 +8705,7 @@
         <v>122144.0</v>
       </c>
       <c r="I180" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="181" ht="11.25" customHeight="1">
@@ -8734,7 +8734,7 @@
         <v>153334.34</v>
       </c>
       <c r="I181" s="22">
-        <v>163535.04</v>
+        <v>161915.88</v>
       </c>
     </row>
     <row r="182" ht="11.25" customHeight="1">
@@ -8763,7 +8763,7 @@
         <v>122144.0</v>
       </c>
       <c r="I182" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="183" ht="11.25" customHeight="1">
@@ -8792,7 +8792,7 @@
         <v>122144.0</v>
       </c>
       <c r="I183" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="184" ht="11.25" customHeight="1">
@@ -8821,7 +8821,7 @@
         <v>122144.0</v>
       </c>
       <c r="I184" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="185" ht="11.25" customHeight="1">
@@ -8850,7 +8850,7 @@
         <v>122144.0</v>
       </c>
       <c r="I185" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="186" ht="11.25" customHeight="1">
@@ -8879,7 +8879,7 @@
         <v>122144.0</v>
       </c>
       <c r="I186" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="187" ht="11.25" customHeight="1">
@@ -8908,7 +8908,7 @@
         <v>122144.0</v>
       </c>
       <c r="I187" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="188" ht="11.25" customHeight="1">
@@ -8937,7 +8937,7 @@
         <v>122144.0</v>
       </c>
       <c r="I188" s="22">
-        <v>130269.73</v>
+        <v>128979.93</v>
       </c>
     </row>
     <row r="189" ht="11.25" customHeight="1">
@@ -8966,7 +8966,7 @@
         <v>113575.22</v>
       </c>
       <c r="I189" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="190" ht="12.0" customHeight="1">
@@ -8995,7 +8995,7 @@
         <v>113575.22</v>
       </c>
       <c r="I190" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="191" ht="12.0" customHeight="1">
@@ -9024,7 +9024,7 @@
         <v>113575.22</v>
       </c>
       <c r="I191" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="192" ht="12.0" customHeight="1">
@@ -9053,7 +9053,7 @@
         <v>113575.22</v>
       </c>
       <c r="I192" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="193" ht="12.0" customHeight="1">
@@ -9082,7 +9082,7 @@
         <v>113575.22</v>
       </c>
       <c r="I193" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="194" ht="12.75" customHeight="1">
@@ -9111,7 +9111,7 @@
         <v>113575.22</v>
       </c>
       <c r="I194" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="195" ht="12.0" customHeight="1">
@@ -9140,7 +9140,7 @@
         <v>107265.49</v>
       </c>
       <c r="I195" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="196" ht="12.0" customHeight="1">
@@ -9169,7 +9169,7 @@
         <v>107265.49</v>
       </c>
       <c r="I196" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="197" ht="12.0" customHeight="1">
@@ -9198,7 +9198,7 @@
         <v>107265.49</v>
       </c>
       <c r="I197" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="198" ht="12.0" customHeight="1">
@@ -9227,7 +9227,7 @@
         <v>107265.49</v>
       </c>
       <c r="I198" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="199" ht="12.0" customHeight="1">
@@ -9256,7 +9256,7 @@
         <v>107265.49</v>
       </c>
       <c r="I199" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="200" ht="12.0" customHeight="1">
@@ -9285,7 +9285,7 @@
         <v>107265.49</v>
       </c>
       <c r="I200" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="201" ht="12.0" customHeight="1">
@@ -9314,7 +9314,7 @@
         <v>107265.49</v>
       </c>
       <c r="I201" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="202" ht="12.75" customHeight="1">
@@ -9343,7 +9343,7 @@
         <v>107265.49</v>
       </c>
       <c r="I202" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="203" ht="12.0" customHeight="1">
@@ -9372,7 +9372,7 @@
         <v>107265.49</v>
       </c>
       <c r="I203" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="204" ht="12.0" customHeight="1">
@@ -9401,7 +9401,7 @@
         <v>107265.49</v>
       </c>
       <c r="I204" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="205" ht="12.0" customHeight="1">
@@ -9430,7 +9430,7 @@
         <v>107265.49</v>
       </c>
       <c r="I205" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="206" ht="12.0" customHeight="1">
@@ -9459,7 +9459,7 @@
         <v>107265.49</v>
       </c>
       <c r="I206" s="22">
-        <v>114401.42</v>
+        <v>113268.73</v>
       </c>
     </row>
     <row r="207" ht="12.0" customHeight="1">
@@ -9488,7 +9488,7 @@
         <v>203678.23</v>
       </c>
       <c r="I207" s="22">
-        <v>217228.1</v>
+        <v>215077.33</v>
       </c>
     </row>
     <row r="208" ht="12.0" customHeight="1">
@@ -9517,7 +9517,7 @@
         <v>118118.23</v>
       </c>
       <c r="I208" s="22">
-        <v>125976.15</v>
+        <v>124728.86</v>
       </c>
     </row>
     <row r="209" ht="12.0" customHeight="1">
@@ -9546,7 +9546,7 @@
         <v>118118.23</v>
       </c>
       <c r="I209" s="22">
-        <v>125976.15</v>
+        <v>124728.86</v>
       </c>
     </row>
     <row r="210" ht="12.0" customHeight="1">
@@ -9575,7 +9575,7 @@
         <v>203678.23</v>
       </c>
       <c r="I210" s="22">
-        <v>217228.1</v>
+        <v>215077.33</v>
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
@@ -9604,7 +9604,7 @@
         <v>113575.22</v>
       </c>
       <c r="I211" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="212" ht="12.0" customHeight="1">
@@ -9633,7 +9633,7 @@
         <v>113575.22</v>
       </c>
       <c r="I212" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="213" ht="12.0" customHeight="1">
@@ -9662,7 +9662,7 @@
         <v>113575.22</v>
       </c>
       <c r="I213" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="214" ht="12.0" customHeight="1">
@@ -9691,7 +9691,7 @@
         <v>113575.22</v>
       </c>
       <c r="I214" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="215" ht="12.0" customHeight="1">
@@ -9720,7 +9720,7 @@
         <v>113575.22</v>
       </c>
       <c r="I215" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="216" ht="12.0" customHeight="1">
@@ -9749,7 +9749,7 @@
         <v>113575.22</v>
       </c>
       <c r="I216" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="217" ht="12.0" customHeight="1">
@@ -9778,7 +9778,7 @@
         <v>113575.22</v>
       </c>
       <c r="I217" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="218" ht="12.0" customHeight="1">
@@ -9807,7 +9807,7 @@
         <v>113575.22</v>
       </c>
       <c r="I218" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="219" ht="12.75" customHeight="1">
@@ -9836,7 +9836,7 @@
         <v>113575.22</v>
       </c>
       <c r="I219" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="220" ht="12.0" customHeight="1">
@@ -9865,7 +9865,7 @@
         <v>113575.22</v>
       </c>
       <c r="I220" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="221" ht="12.0" customHeight="1">
@@ -9894,7 +9894,7 @@
         <v>113575.22</v>
       </c>
       <c r="I221" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="222" ht="12.0" customHeight="1">
@@ -9923,7 +9923,7 @@
         <v>113575.22</v>
       </c>
       <c r="I222" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="223" ht="12.0" customHeight="1">
@@ -9952,7 +9952,7 @@
         <v>113575.22</v>
       </c>
       <c r="I223" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="224" ht="12.0" customHeight="1">
@@ -9981,7 +9981,7 @@
         <v>113575.22</v>
       </c>
       <c r="I224" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="225" ht="12.0" customHeight="1">
@@ -10010,7 +10010,7 @@
         <v>113575.22</v>
       </c>
       <c r="I225" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="226" ht="12.0" customHeight="1">
@@ -10039,7 +10039,7 @@
         <v>113575.22</v>
       </c>
       <c r="I226" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="227" ht="12.75" customHeight="1">
@@ -10068,7 +10068,7 @@
         <v>113575.22</v>
       </c>
       <c r="I227" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="228" ht="12.0" customHeight="1">
@@ -10097,7 +10097,7 @@
         <v>113575.22</v>
       </c>
       <c r="I228" s="22">
-        <v>121130.91</v>
+        <v>119931.59</v>
       </c>
     </row>
     <row r="229" ht="12.0" customHeight="1">
@@ -10126,7 +10126,7 @@
         <v>203678.23</v>
       </c>
       <c r="I229" s="22">
-        <v>217228.1</v>
+        <v>215077.33</v>
       </c>
     </row>
     <row r="230" ht="12.0" customHeight="1">
@@ -10155,7 +10155,7 @@
         <v>118118.23</v>
       </c>
       <c r="I230" s="22">
-        <v>125976.15</v>
+        <v>124728.86</v>
       </c>
     </row>
     <row r="231" ht="12.0" customHeight="1">
@@ -10184,7 +10184,7 @@
         <v>118118.23</v>
       </c>
       <c r="I231" s="22">
-        <v>125976.15</v>
+        <v>124728.86</v>
       </c>
     </row>
     <row r="232" ht="12.0" customHeight="1">
@@ -10213,7 +10213,7 @@
         <v>203678.23</v>
       </c>
       <c r="I232" s="22">
-        <v>217228.1</v>
+        <v>215077.33</v>
       </c>
     </row>
     <row r="233" ht="12.0" customHeight="1">
@@ -10242,7 +10242,7 @@
         <v>190849.99</v>
       </c>
       <c r="I233" s="22">
-        <v>203546.45</v>
+        <v>201531.14</v>
       </c>
     </row>
     <row r="234" ht="12.0" customHeight="1">
@@ -10271,7 +10271,7 @@
         <v>122689.28</v>
       </c>
       <c r="I234" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="235" ht="12.0" customHeight="1">
@@ -10300,7 +10300,7 @@
         <v>122689.28</v>
       </c>
       <c r="I235" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="236" ht="12.75" customHeight="1">
@@ -10329,7 +10329,7 @@
         <v>122689.28</v>
       </c>
       <c r="I236" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="237" ht="12.0" customHeight="1">
@@ -10358,7 +10358,7 @@
         <v>122689.28</v>
       </c>
       <c r="I237" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="238" ht="12.0" customHeight="1">
@@ -10387,7 +10387,7 @@
         <v>122689.28</v>
       </c>
       <c r="I238" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="239" ht="12.0" customHeight="1">
@@ -10416,7 +10416,7 @@
         <v>122689.28</v>
       </c>
       <c r="I239" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="240" ht="12.0" customHeight="1">
@@ -10445,7 +10445,7 @@
         <v>122689.28</v>
       </c>
       <c r="I240" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="241" ht="12.0" customHeight="1">
@@ -10474,7 +10474,7 @@
         <v>122689.28</v>
       </c>
       <c r="I241" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="242" ht="12.0" customHeight="1">
@@ -10503,7 +10503,7 @@
         <v>122689.28</v>
       </c>
       <c r="I242" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="243" ht="12.0" customHeight="1">
@@ -10532,7 +10532,7 @@
         <v>122689.28</v>
       </c>
       <c r="I243" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="244" ht="12.75" customHeight="1">
@@ -10561,7 +10561,7 @@
         <v>122689.28</v>
       </c>
       <c r="I244" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="245" ht="12.0" customHeight="1">
@@ -10590,7 +10590,7 @@
         <v>122689.28</v>
       </c>
       <c r="I245" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="246" ht="12.0" customHeight="1">
@@ -10619,7 +10619,7 @@
         <v>122689.28</v>
       </c>
       <c r="I246" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="247" ht="12.0" customHeight="1">
@@ -10648,7 +10648,7 @@
         <v>122689.28</v>
       </c>
       <c r="I247" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="248" ht="12.0" customHeight="1">
@@ -10677,7 +10677,7 @@
         <v>122689.28</v>
       </c>
       <c r="I248" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="249" ht="12.0" customHeight="1">
@@ -10706,7 +10706,7 @@
         <v>122689.28</v>
       </c>
       <c r="I249" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="250" ht="12.0" customHeight="1">
@@ -10735,7 +10735,7 @@
         <v>122689.28</v>
       </c>
       <c r="I250" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="251" ht="12.0" customHeight="1">
@@ -10764,7 +10764,7 @@
         <v>122689.28</v>
       </c>
       <c r="I251" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="252" ht="12.0" customHeight="1">
@@ -10793,7 +10793,7 @@
         <v>122689.28</v>
       </c>
       <c r="I252" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="253" ht="12.0" customHeight="1">
@@ -10822,7 +10822,7 @@
         <v>122689.28</v>
       </c>
       <c r="I253" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="254" ht="12.0" customHeight="1">
@@ -10851,7 +10851,7 @@
         <v>190849.99</v>
       </c>
       <c r="I254" s="22">
-        <v>203546.45</v>
+        <v>201531.14</v>
       </c>
     </row>
     <row r="255" ht="11.25" customHeight="1">
@@ -10876,7 +10876,7 @@
         <v>211298.21</v>
       </c>
       <c r="I255" s="22">
-        <v>225355.0</v>
+        <v>223123.77</v>
       </c>
     </row>
     <row r="256" ht="11.25" customHeight="1">
@@ -10905,7 +10905,7 @@
         <v>122689.28</v>
       </c>
       <c r="I256" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="257" ht="11.25" customHeight="1">
@@ -10934,7 +10934,7 @@
         <v>122689.28</v>
       </c>
       <c r="I257" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="258" ht="11.25" customHeight="1">
@@ -10963,7 +10963,7 @@
         <v>211298.21</v>
       </c>
       <c r="I258" s="22">
-        <v>225355.0</v>
+        <v>223123.77</v>
       </c>
     </row>
     <row r="259" ht="12.0" customHeight="1">
@@ -10992,7 +10992,7 @@
         <v>122689.28</v>
       </c>
       <c r="I259" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="260" ht="11.25" customHeight="1">
@@ -11021,7 +11021,7 @@
         <v>122689.28</v>
       </c>
       <c r="I260" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="261" ht="11.25" customHeight="1">
@@ -11050,7 +11050,7 @@
         <v>122689.28</v>
       </c>
       <c r="I261" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="262" ht="11.25" customHeight="1">
@@ -11079,7 +11079,7 @@
         <v>122689.28</v>
       </c>
       <c r="I262" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="263" ht="11.25" customHeight="1">
@@ -11108,7 +11108,7 @@
         <v>122689.28</v>
       </c>
       <c r="I263" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="264" ht="11.25" customHeight="1">
@@ -11137,7 +11137,7 @@
         <v>122705.64</v>
       </c>
       <c r="I264" s="22">
-        <v>130868.74</v>
+        <v>129573.01</v>
       </c>
     </row>
     <row r="265" ht="11.25" customHeight="1">
@@ -11166,7 +11166,7 @@
         <v>157505.77</v>
       </c>
       <c r="I265" s="22">
-        <v>167983.98</v>
+        <v>166320.77</v>
       </c>
     </row>
     <row r="266" ht="11.25" customHeight="1">
@@ -11195,7 +11195,7 @@
         <v>157505.77</v>
       </c>
       <c r="I266" s="22">
-        <v>167983.98</v>
+        <v>166320.77</v>
       </c>
     </row>
     <row r="267" ht="11.25" customHeight="1">
@@ -11224,7 +11224,7 @@
         <v>157505.77</v>
       </c>
       <c r="I267" s="22">
-        <v>167983.98</v>
+        <v>166320.77</v>
       </c>
     </row>
     <row r="268" ht="11.25" customHeight="1">
@@ -11253,7 +11253,7 @@
         <v>122689.28</v>
       </c>
       <c r="I268" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="269" ht="11.25" customHeight="1">
@@ -11282,7 +11282,7 @@
         <v>122689.28</v>
       </c>
       <c r="I269" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="270" ht="11.25" customHeight="1">
@@ -11311,7 +11311,7 @@
         <v>122689.28</v>
       </c>
       <c r="I270" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="271" ht="11.25" customHeight="1">
@@ -11340,7 +11340,7 @@
         <v>122689.28</v>
       </c>
       <c r="I271" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="272" ht="11.25" customHeight="1">
@@ -11369,7 +11369,7 @@
         <v>122689.28</v>
       </c>
       <c r="I272" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="273" ht="11.25" customHeight="1">
@@ -11398,7 +11398,7 @@
         <v>122689.28</v>
       </c>
       <c r="I273" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="274" ht="11.25" customHeight="1">
@@ -11427,7 +11427,7 @@
         <v>122689.28</v>
       </c>
       <c r="I274" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="275" ht="11.25" customHeight="1">
@@ -11456,7 +11456,7 @@
         <v>122689.28</v>
       </c>
       <c r="I275" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="276" ht="11.25" customHeight="1">
@@ -11485,7 +11485,7 @@
         <v>122689.28</v>
       </c>
       <c r="I276" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="277" ht="11.25" customHeight="1">
@@ -11514,7 +11514,7 @@
         <v>122689.28</v>
       </c>
       <c r="I277" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="278" ht="11.25" customHeight="1">
@@ -11543,7 +11543,7 @@
         <v>122689.28</v>
       </c>
       <c r="I278" s="22">
-        <v>130851.29</v>
+        <v>129555.73</v>
       </c>
     </row>
     <row r="279" ht="11.25" customHeight="1">
@@ -11572,7 +11572,7 @@
         <v>163585.71</v>
       </c>
       <c r="I279" s="22">
-        <v>174468.39</v>
+        <v>172740.98</v>
       </c>
     </row>
     <row r="280" ht="11.25" customHeight="1">
@@ -11601,7 +11601,7 @@
         <v>116910.5</v>
       </c>
       <c r="I280" s="22">
-        <v>124688.07</v>
+        <v>123453.54</v>
       </c>
     </row>
     <row r="281" ht="11.25" customHeight="1">
@@ -11630,7 +11630,7 @@
         <v>116910.5</v>
       </c>
       <c r="I281" s="22">
-        <v>124688.07</v>
+        <v>123453.54</v>
       </c>
     </row>
     <row r="282" ht="11.25" customHeight="1">
@@ -11655,7 +11655,7 @@
         <v>221360.03</v>
       </c>
       <c r="I282" s="22">
-        <v>236086.19</v>
+        <v>233748.71</v>
       </c>
     </row>
     <row r="283" ht="11.25" customHeight="1">
@@ -11684,7 +11684,7 @@
         <v>128531.63</v>
       </c>
       <c r="I283" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="284" ht="11.25" customHeight="1">
@@ -11713,7 +11713,7 @@
         <v>128531.63</v>
       </c>
       <c r="I284" s="22">
-        <v>137082.31</v>
+        <v>135725.06</v>
       </c>
     </row>
     <row r="285" ht="11.25" customHeight="1">
@@ -11742,7 +11742,7 @@
         <v>221360.03</v>
       </c>
       <c r="I285" s="22">
-        <v>236086.19</v>
+        <v>233748.71</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1"/>
